--- a/reports/jobs_2026-08-23.xlsx
+++ b/reports/jobs_2026-08-23.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1930,17 +1930,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Ai Engg Intern</t>
+          <t>Software Development Engineer I United States - Washington - Seattle Technology</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1948,11 +1948,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
@@ -1960,12 +1956,12 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
+          <t>https://careers.expediagroup.com/job/software-development-engineer-i/seattle-wa/R-108739/</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1982,7 +1978,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>Ai Engg Intern</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2007,7 +2003,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2029,7 +2025,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>GenAI Product Builder Intern</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2054,7 +2050,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2071,17 +2067,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Freshworks</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Specialist - Data Platform Engineering</t>
+          <t>GenAI Product Builder Intern</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2091,7 +2087,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Chennai, in</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2101,12 +2097,12 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
+          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/Freshworks</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2118,17 +2114,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Freshworks</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Specialist - Data Platform Engineering</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2136,7 +2132,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Chennai, in</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/Freshworks</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2204,12 +2204,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2222,11 +2222,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Hyderabad, Telangana, India</t>
-        </is>
-      </c>
+      <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
@@ -2234,12 +2230,12 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2251,12 +2247,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2271,7 +2267,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2281,12 +2277,12 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2303,12 +2299,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (Agent Intelligence &amp; Evaluations)</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2328,7 +2324,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143976319</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2350,12 +2346,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Software Engineer - 2 Backend</t>
+          <t>Machine Learning Engineer (Agent Intelligence &amp; Evaluations)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2365,7 +2361,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2375,7 +2371,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143738909</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143976319</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2392,12 +2388,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t xml:space="preserve"> Software Engineer - 2 Backend</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2412,7 +2408,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2422,12 +2418,12 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143738909</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2439,17 +2435,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Licious</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>By: Licious DevOps</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2457,7 +2453,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>https://careers.licious.com/author/adminlic/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://www.licious.in/careers</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Licious</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>By: Licious DevOps</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://careers.licious.com/author/adminlic/</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://www.licious.in/careers</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2568,17 +2568,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Automation engineer (Warehouse Automation)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2586,11 +2586,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
@@ -2598,12 +2594,12 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/fe839191-1761-4094-9d3c-4d554904b84d</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2620,12 +2616,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>GTM Engineer – Meesho AI Services (MAS)</t>
+          <t>Automation engineer (Warehouse Automation)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2645,7 +2641,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c49e13f6-f027-42f3-98b5-745d83997cbf</t>
+          <t>https://jobs.lever.co/meesho/fe839191-1761-4094-9d3c-4d554904b84d</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2667,7 +2663,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>GTM Engineer – Meesho AI Services (MAS)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2692,7 +2688,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://jobs.lever.co/meesho/c49e13f6-f027-42f3-98b5-745d83997cbf</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2709,12 +2705,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2727,7 +2723,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
@@ -2735,12 +2735,12 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2752,17 +2752,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2795,17 +2795,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Operations - Internship</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2856,11 +2856,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
@@ -2868,12 +2864,12 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/6c1b9af2-9a7c-4cd2-a97b-54e956cf82f1</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2890,7 +2886,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Admin &amp; Operations - Internship</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2905,7 +2901,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2915,7 +2911,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://jobs.lever.co/paytm/6c1b9af2-9a7c-4cd2-a97b-54e956cf82f1</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2937,7 +2933,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Product Management - Intern</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2952,7 +2948,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2962,7 +2958,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/1155c0e3-bf03-4b46-97f0-44673b6518f7</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2984,7 +2980,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Product Management - Intern - Telco.</t>
+          <t>Product Management - Intern</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3009,7 +3005,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
+          <t>https://jobs.lever.co/paytm/1155c0e3-bf03-4b46-97f0-44673b6518f7</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3031,7 +3027,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Product Management Intern- Insurance</t>
+          <t>Product Management - Intern - Telco.</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3041,7 +3037,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>recent graduate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3056,7 +3052,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
+          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3078,7 +3074,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Product Management Intern- Insurance</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3088,7 +3084,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>recent graduate</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3103,7 +3099,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
+          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3120,17 +3116,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>PhonePe</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>AI Video Specialist</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3140,7 +3136,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -3150,12 +3146,12 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7735150003</t>
+          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/phonepe</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -3172,7 +3168,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Firmware Engineer(5-7 years)</t>
+          <t>AI Video Specialist</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3197,7 +3193,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7765845003</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7735150003</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3219,17 +3215,17 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Service Delivery Engineer, SRE</t>
+          <t>Firmware Engineer(5-7 years)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>1-3 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3244,7 +3240,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7762335003</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7765845003</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3266,7 +3262,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - 2</t>
+          <t>Service Delivery Engineer, SRE</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3276,7 +3272,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>1-3 years</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3291,7 +3287,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7766868003</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7762335003</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3313,17 +3309,17 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Android</t>
+          <t>Site Reliability Engineer - 2</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>1-2 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3338,7 +3334,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7799494003</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7766868003</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3355,25 +3351,29 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>PhonePe</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Software Engineer, Android</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr"/>
+          <t>1-2 years</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
@@ -3381,12 +3381,12 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7799494003</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://boards.greenhouse.io/phonepe</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3398,17 +3398,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3416,11 +3416,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
@@ -3428,12 +3424,12 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3450,12 +3446,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3475,7 +3471,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3497,12 +3493,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3522,7 +3518,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3539,17 +3535,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3557,7 +3553,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
@@ -3565,12 +3565,12 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3582,17 +3582,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3600,11 +3600,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
@@ -3612,12 +3608,12 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3634,12 +3630,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Builder</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3659,7 +3655,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3676,17 +3672,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Industrial Trainee</t>
+          <t>Full Stack Builder</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3696,7 +3692,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -3706,12 +3702,12 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8083001?gh_jid=8083001</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3728,7 +3724,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Payroll Industrial Trainee</t>
+          <t>Industrial Trainee</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3753,7 +3749,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8083001?gh_jid=8083001</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3770,17 +3766,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Sarvam AI</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Vision</t>
+          <t>Payroll Industrial Trainee</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3790,7 +3786,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3800,12 +3796,12 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam/282019f4-f86b-4fe0-a643-bbac0cd8a751</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -3817,17 +3813,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Sarvam AI</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Machine Learning Engineer, Vision</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3837,7 +3833,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Remote Instructor- Python</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -3847,12 +3843,12 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://jobs.ashbyhq.com/sarvam/282019f4-f86b-4fe0-a643-bbac0cd8a751</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://jobs.ashbyhq.com/sarvam</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -3864,17 +3860,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3882,7 +3878,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Remote Instructor- Python</t>
+        </is>
+      </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
@@ -3890,12 +3890,12 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjksInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTYsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjksInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTYsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation(Tamil)</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MDUsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Video Editor- AI</t>
+          <t>Intern - Content Moderation(Tamil)</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MDUsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4079,17 +4079,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Video Editor- AI</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4097,11 +4097,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
@@ -4109,12 +4105,12 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4131,12 +4127,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4156,7 +4152,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4173,17 +4169,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Snowflake India</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Account Engineer</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -4193,7 +4189,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>CO-Colombia-Remote</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4203,12 +4199,12 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4220,17 +4216,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>Snowflake India</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Account Engineer</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -4238,7 +4234,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>CO-Colombia-Remote</t>
+        </is>
+      </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
@@ -4246,12 +4246,12 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://jobs.ashbyhq.com/snowflake</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4263,17 +4263,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -4281,11 +4281,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
@@ -4293,12 +4289,12 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4315,12 +4311,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Test Jerin</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4340,7 +4336,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4357,48 +4353,95 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
           <t>upGrad</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Data Science Bootcamp with AI</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
         <is>
           <t>https://www.upgrad.com/bootcamps/job-linked-data-science-advanced-bootcamp/</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>https://www.upgrad.com/careers/</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I86"/>
+  <autoFilter ref="A1:I87"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4485,6 +4528,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4496,7 +4540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4584,15 +4628,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Vymo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://getvymo.com/careers/</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://getvymo.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4601,18 +4665,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -4621,18 +4685,38 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Juspay</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://juspay.io/careers</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://juspay.io/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4641,18 +4725,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>FirstCry</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://www.firstcry.com/careers</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4661,18 +4745,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -4681,18 +4765,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4701,18 +4785,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4721,18 +4805,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4741,6 +4825,26 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Newgen Software</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://newgensoft.com/careers/</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://newgensoft.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
